--- a/content/WtA Супер-Сэнтай Рюкю/генережка тигры.xlsx
+++ b/content/WtA Супер-Сэнтай Рюкю/генережка тигры.xlsx
@@ -1,22 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Obsidian Circe\Rolling Vault\WtA Супер-Сэнтай Рюкю\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19375663-BE9A-48A3-9E41-DED34EC0DB0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{498EE635-38A1-4EA7-B017-10DEDBAE6F0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="314" windowWidth="25370" windowHeight="13759" xr2:uid="{8C796DC0-0E5B-43FF-B2DD-E20750249270}"/>
+    <workbookView xWindow="-118" yWindow="-118" windowWidth="25370" windowHeight="13759" activeTab="1" xr2:uid="{8C796DC0-0E5B-43FF-B2DD-E20750249270}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
+    <sheet name="Лист2" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Лист1!$G$20:$S$20</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Лист2!$A$1:$H$4</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -28,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="219" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="290" uniqueCount="117">
   <si>
     <t>Атрибут</t>
   </si>
@@ -354,11 +356,62 @@
   <si>
     <t>Вышла за бюджет</t>
   </si>
+  <si>
+    <t>Роль</t>
+  </si>
+  <si>
+    <t>Фонарь</t>
+  </si>
+  <si>
+    <t>Кулак</t>
+  </si>
+  <si>
+    <t>Зеркало</t>
+  </si>
+  <si>
+    <t>Лист</t>
+  </si>
+  <si>
+    <t>Колонна</t>
+  </si>
+  <si>
+    <t>Почет</t>
+  </si>
+  <si>
+    <t>Слава</t>
+  </si>
+  <si>
+    <t>Достоинство</t>
+  </si>
+  <si>
+    <t>Мудрость</t>
+  </si>
+  <si>
+    <t>Старт</t>
+  </si>
+  <si>
+    <t>на 2 ранг</t>
+  </si>
+  <si>
+    <t>дельта</t>
+  </si>
+  <si>
+    <t>сейчас</t>
+  </si>
+  <si>
+    <t>Сумма</t>
+  </si>
+  <si>
+    <t>с кагуей</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="165" formatCode="0.0%"/>
+  </numFmts>
   <fonts count="17" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -502,7 +555,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="11">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -539,6 +592,30 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -558,11 +635,12 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1"/>
@@ -630,10 +708,19 @@
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="9" fontId="0" fillId="4" borderId="0" xfId="2" applyFont="1" applyFill="1"/>
+    <xf numFmtId="165" fontId="0" fillId="6" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1"/>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="3">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
     <cellStyle name="Обычный 2" xfId="1" xr:uid="{8FDA4460-39BB-40B1-9483-50C7FBA2CEAC}"/>
+    <cellStyle name="Процентный" xfId="2" builtinId="5"/>
   </cellStyles>
   <dxfs count="19">
     <dxf>
@@ -3879,4 +3966,874 @@
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CE09EE5F-97FE-4687-8367-923B1D05EB4F}">
+  <dimension ref="A1:L23"/>
+  <sheetFormatPr defaultRowHeight="15.05" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="11.21875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="4.77734375" customWidth="1"/>
+    <col min="9" max="9" width="4.77734375" customWidth="1"/>
+    <col min="12" max="12" width="5.77734375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>101</v>
+      </c>
+      <c r="B1" t="s">
+        <v>107</v>
+      </c>
+      <c r="C1" t="s">
+        <v>111</v>
+      </c>
+      <c r="D1" t="s">
+        <v>112</v>
+      </c>
+      <c r="E1" t="s">
+        <v>113</v>
+      </c>
+      <c r="F1" s="40"/>
+      <c r="G1" t="s">
+        <v>114</v>
+      </c>
+      <c r="H1" t="s">
+        <v>113</v>
+      </c>
+      <c r="I1" s="40"/>
+      <c r="J1" t="s">
+        <v>116</v>
+      </c>
+      <c r="K1" t="s">
+        <v>113</v>
+      </c>
+      <c r="L1" s="40"/>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A2" s="36" t="s">
+        <v>102</v>
+      </c>
+      <c r="B2" s="36" t="s">
+        <v>108</v>
+      </c>
+      <c r="C2" s="36">
+        <v>0</v>
+      </c>
+      <c r="D2" s="36">
+        <v>2</v>
+      </c>
+      <c r="E2" s="36">
+        <f>$D2-C2</f>
+        <v>2</v>
+      </c>
+      <c r="F2" s="40"/>
+      <c r="G2" s="36">
+        <v>0.2</v>
+      </c>
+      <c r="H2" s="36">
+        <f>$D2-G2</f>
+        <v>1.8</v>
+      </c>
+      <c r="I2" s="41">
+        <f>1-H2/$D2</f>
+        <v>9.9999999999999978E-2</v>
+      </c>
+      <c r="J2" s="36">
+        <f>G2</f>
+        <v>0.2</v>
+      </c>
+      <c r="K2" s="36">
+        <f>$D2-J2</f>
+        <v>1.8</v>
+      </c>
+      <c r="L2" s="41">
+        <f>1-K2/$D2</f>
+        <v>9.9999999999999978E-2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A3" s="37" t="s">
+        <v>102</v>
+      </c>
+      <c r="B3" s="37" t="s">
+        <v>109</v>
+      </c>
+      <c r="C3" s="37">
+        <v>3</v>
+      </c>
+      <c r="D3" s="37">
+        <v>5</v>
+      </c>
+      <c r="E3" s="37">
+        <f t="shared" ref="E3:E4" si="0">$D3-C3</f>
+        <v>2</v>
+      </c>
+      <c r="F3" s="40"/>
+      <c r="G3" s="37">
+        <v>0.3</v>
+      </c>
+      <c r="H3" s="37">
+        <f>$D3-G3</f>
+        <v>4.7</v>
+      </c>
+      <c r="I3" s="41">
+        <f t="shared" ref="I3:I4" si="1">1-H3/$D3</f>
+        <v>5.9999999999999942E-2</v>
+      </c>
+      <c r="J3" s="37">
+        <f>G3</f>
+        <v>0.3</v>
+      </c>
+      <c r="K3" s="37">
+        <f>$D3-J3</f>
+        <v>4.7</v>
+      </c>
+      <c r="L3" s="41">
+        <f t="shared" ref="L3:L4" si="2">1-K3/$D3</f>
+        <v>5.9999999999999942E-2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A4" s="35" t="s">
+        <v>102</v>
+      </c>
+      <c r="B4" s="35" t="s">
+        <v>110</v>
+      </c>
+      <c r="C4" s="35">
+        <v>0</v>
+      </c>
+      <c r="D4" s="35">
+        <v>1</v>
+      </c>
+      <c r="E4" s="35">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="F4" s="40"/>
+      <c r="G4" s="35">
+        <v>0.2</v>
+      </c>
+      <c r="H4" s="35">
+        <f>$D4-G4</f>
+        <v>0.8</v>
+      </c>
+      <c r="I4" s="41">
+        <f t="shared" si="1"/>
+        <v>0.19999999999999996</v>
+      </c>
+      <c r="J4" s="35">
+        <v>1</v>
+      </c>
+      <c r="K4" s="35">
+        <f>$D4-J4</f>
+        <v>0</v>
+      </c>
+      <c r="L4" s="41">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A5" s="39"/>
+      <c r="B5" s="39"/>
+      <c r="C5" s="39"/>
+      <c r="D5" s="39"/>
+      <c r="E5" s="39"/>
+      <c r="F5" s="40"/>
+      <c r="G5" s="39"/>
+      <c r="H5" s="39"/>
+      <c r="I5" s="42">
+        <f>1-SUM(H2:H4)/SUM($D2:$D4)</f>
+        <v>8.7500000000000022E-2</v>
+      </c>
+      <c r="J5" s="39"/>
+      <c r="K5" s="39"/>
+      <c r="L5" s="42">
+        <f>1-SUM(K2:K4)/SUM($D2:$D4)</f>
+        <v>0.1875</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>101</v>
+      </c>
+      <c r="B6" t="s">
+        <v>107</v>
+      </c>
+      <c r="C6" t="s">
+        <v>111</v>
+      </c>
+      <c r="D6" t="s">
+        <v>112</v>
+      </c>
+      <c r="E6" t="s">
+        <v>113</v>
+      </c>
+      <c r="F6" s="40"/>
+      <c r="G6" t="s">
+        <v>114</v>
+      </c>
+      <c r="H6" t="s">
+        <v>113</v>
+      </c>
+      <c r="I6" s="40"/>
+      <c r="J6" t="s">
+        <v>114</v>
+      </c>
+      <c r="K6" t="s">
+        <v>113</v>
+      </c>
+      <c r="L6" s="40"/>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A7" s="36" t="s">
+        <v>103</v>
+      </c>
+      <c r="B7" s="36" t="s">
+        <v>108</v>
+      </c>
+      <c r="C7" s="36">
+        <v>2</v>
+      </c>
+      <c r="D7" s="36">
+        <v>5</v>
+      </c>
+      <c r="E7" s="36">
+        <f>$D7-C7</f>
+        <v>3</v>
+      </c>
+      <c r="F7" s="40"/>
+      <c r="G7" s="36"/>
+      <c r="H7" s="36">
+        <f>$D7-G7</f>
+        <v>5</v>
+      </c>
+      <c r="I7" s="41">
+        <f>1-H7/$D7</f>
+        <v>0</v>
+      </c>
+      <c r="J7" s="36">
+        <f>G7</f>
+        <v>0</v>
+      </c>
+      <c r="K7" s="36">
+        <f>$D7-J7</f>
+        <v>5</v>
+      </c>
+      <c r="L7" s="41">
+        <f>1-K7/$D7</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A8" s="37" t="s">
+        <v>103</v>
+      </c>
+      <c r="B8" s="37" t="s">
+        <v>109</v>
+      </c>
+      <c r="C8" s="37">
+        <v>1</v>
+      </c>
+      <c r="D8" s="37">
+        <v>3</v>
+      </c>
+      <c r="E8" s="37">
+        <f t="shared" ref="E8:E9" si="3">$D8-C8</f>
+        <v>2</v>
+      </c>
+      <c r="F8" s="40"/>
+      <c r="G8" s="37"/>
+      <c r="H8" s="37">
+        <f>$D8-G8</f>
+        <v>3</v>
+      </c>
+      <c r="I8" s="41">
+        <f t="shared" ref="I8:I9" si="4">1-H8/$D8</f>
+        <v>0</v>
+      </c>
+      <c r="J8" s="37">
+        <f>G8</f>
+        <v>0</v>
+      </c>
+      <c r="K8" s="37">
+        <f>$D8-J8</f>
+        <v>3</v>
+      </c>
+      <c r="L8" s="41">
+        <f t="shared" ref="L8:L9" si="5">1-K8/$D8</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A9" s="35" t="s">
+        <v>103</v>
+      </c>
+      <c r="B9" s="35" t="s">
+        <v>110</v>
+      </c>
+      <c r="C9" s="35">
+        <v>0</v>
+      </c>
+      <c r="D9" s="35">
+        <v>1</v>
+      </c>
+      <c r="E9" s="35">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="F9" s="40"/>
+      <c r="G9" s="35"/>
+      <c r="H9" s="35">
+        <f>$D9-G9</f>
+        <v>1</v>
+      </c>
+      <c r="I9" s="41">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J9" s="35">
+        <f>G9+1</f>
+        <v>1</v>
+      </c>
+      <c r="K9" s="35">
+        <f>$D9-J9</f>
+        <v>0</v>
+      </c>
+      <c r="L9" s="41">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A10" s="39"/>
+      <c r="B10" s="39"/>
+      <c r="C10" s="39"/>
+      <c r="D10" s="39"/>
+      <c r="E10" s="39"/>
+      <c r="F10" s="40"/>
+      <c r="G10" s="39"/>
+      <c r="H10" s="39"/>
+      <c r="I10" s="42">
+        <f>1-SUM(H7:H9)/SUM($D7:$D9)</f>
+        <v>0</v>
+      </c>
+      <c r="J10" s="39"/>
+      <c r="K10" s="39"/>
+      <c r="L10" s="42">
+        <f>1-SUM(K7:K9)/SUM($D7:$D9)</f>
+        <v>0.11111111111111116</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>101</v>
+      </c>
+      <c r="B11" t="s">
+        <v>107</v>
+      </c>
+      <c r="C11" t="s">
+        <v>111</v>
+      </c>
+      <c r="D11" t="s">
+        <v>112</v>
+      </c>
+      <c r="E11" t="s">
+        <v>113</v>
+      </c>
+      <c r="F11" s="40"/>
+      <c r="G11" t="s">
+        <v>114</v>
+      </c>
+      <c r="H11" t="s">
+        <v>113</v>
+      </c>
+      <c r="I11" s="40"/>
+      <c r="J11" t="s">
+        <v>114</v>
+      </c>
+      <c r="K11" t="s">
+        <v>113</v>
+      </c>
+      <c r="L11" s="40"/>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A12" s="38" t="s">
+        <v>105</v>
+      </c>
+      <c r="B12" s="38" t="s">
+        <v>115</v>
+      </c>
+      <c r="C12" s="38">
+        <v>3</v>
+      </c>
+      <c r="D12" s="38">
+        <v>9</v>
+      </c>
+      <c r="E12" s="38">
+        <f>$D12-C12</f>
+        <v>6</v>
+      </c>
+      <c r="F12" s="40"/>
+      <c r="G12" s="38">
+        <f>0.3+0.3+0.1</f>
+        <v>0.7</v>
+      </c>
+      <c r="H12" s="38">
+        <f>$D12-G12</f>
+        <v>8.3000000000000007</v>
+      </c>
+      <c r="I12" s="41">
+        <f>1-H12/$D12</f>
+        <v>7.7777777777777724E-2</v>
+      </c>
+      <c r="J12" s="38">
+        <f>G12+1</f>
+        <v>1.7</v>
+      </c>
+      <c r="K12" s="38">
+        <f>$D12-J12</f>
+        <v>7.3</v>
+      </c>
+      <c r="L12" s="41">
+        <f>1-K12/$D12</f>
+        <v>0.18888888888888888</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A13" s="39"/>
+      <c r="B13" s="39"/>
+      <c r="C13" s="39"/>
+      <c r="D13" s="39"/>
+      <c r="E13" s="39"/>
+      <c r="F13" s="40"/>
+      <c r="G13" s="39"/>
+      <c r="H13" s="39"/>
+      <c r="I13" s="42">
+        <f>1-SUM(H10:H12)/SUM($D10:$D12)</f>
+        <v>7.7777777777777724E-2</v>
+      </c>
+      <c r="J13" s="39"/>
+      <c r="K13" s="39"/>
+      <c r="L13" s="42">
+        <f>1-SUM(K10:K12)/SUM($D10:$D12)</f>
+        <v>0.18888888888888888</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>101</v>
+      </c>
+      <c r="B14" t="s">
+        <v>107</v>
+      </c>
+      <c r="C14" t="s">
+        <v>111</v>
+      </c>
+      <c r="D14" t="s">
+        <v>112</v>
+      </c>
+      <c r="E14" t="s">
+        <v>113</v>
+      </c>
+      <c r="F14" s="40"/>
+      <c r="G14" t="s">
+        <v>114</v>
+      </c>
+      <c r="H14" t="s">
+        <v>113</v>
+      </c>
+      <c r="I14" s="40"/>
+      <c r="J14" t="s">
+        <v>114</v>
+      </c>
+      <c r="K14" t="s">
+        <v>113</v>
+      </c>
+      <c r="L14" s="40"/>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A15" s="36" t="s">
+        <v>104</v>
+      </c>
+      <c r="B15" s="36" t="s">
+        <v>108</v>
+      </c>
+      <c r="C15" s="36">
+        <v>0</v>
+      </c>
+      <c r="D15" s="36">
+        <v>1</v>
+      </c>
+      <c r="E15" s="36">
+        <f>$D15-C15</f>
+        <v>1</v>
+      </c>
+      <c r="F15" s="40"/>
+      <c r="G15" s="36"/>
+      <c r="H15" s="36">
+        <f>$D15-G15</f>
+        <v>1</v>
+      </c>
+      <c r="I15" s="41">
+        <f>1-H15/$D15</f>
+        <v>0</v>
+      </c>
+      <c r="J15" s="36">
+        <f>G15</f>
+        <v>0</v>
+      </c>
+      <c r="K15" s="36">
+        <f>$D15-J15</f>
+        <v>1</v>
+      </c>
+      <c r="L15" s="41">
+        <f>1-K15/$D15</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A16" s="37" t="s">
+        <v>104</v>
+      </c>
+      <c r="B16" s="37" t="s">
+        <v>109</v>
+      </c>
+      <c r="C16" s="37">
+        <v>0</v>
+      </c>
+      <c r="D16" s="37">
+        <v>1</v>
+      </c>
+      <c r="E16" s="37">
+        <f t="shared" ref="E16:E17" si="6">$D16-C16</f>
+        <v>1</v>
+      </c>
+      <c r="F16" s="40"/>
+      <c r="G16" s="37"/>
+      <c r="H16" s="37">
+        <f>$D16-G16</f>
+        <v>1</v>
+      </c>
+      <c r="I16" s="41">
+        <f t="shared" ref="I16:I17" si="7">1-H16/$D16</f>
+        <v>0</v>
+      </c>
+      <c r="J16" s="37">
+        <f>G16</f>
+        <v>0</v>
+      </c>
+      <c r="K16" s="37">
+        <f>$D16-J16</f>
+        <v>1</v>
+      </c>
+      <c r="L16" s="41">
+        <f t="shared" ref="L16:L17" si="8">1-K16/$D16</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A17" s="35" t="s">
+        <v>104</v>
+      </c>
+      <c r="B17" s="35" t="s">
+        <v>110</v>
+      </c>
+      <c r="C17" s="35">
+        <v>3</v>
+      </c>
+      <c r="D17" s="35">
+        <v>5</v>
+      </c>
+      <c r="E17" s="35">
+        <f t="shared" si="6"/>
+        <v>2</v>
+      </c>
+      <c r="F17" s="40"/>
+      <c r="G17" s="35"/>
+      <c r="H17" s="35">
+        <f>$D17-G17</f>
+        <v>5</v>
+      </c>
+      <c r="I17" s="41">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="J17" s="35">
+        <f>G17+1</f>
+        <v>1</v>
+      </c>
+      <c r="K17" s="35">
+        <f>$D17-J17</f>
+        <v>4</v>
+      </c>
+      <c r="L17" s="41">
+        <f t="shared" si="8"/>
+        <v>0.19999999999999996</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A18" s="39"/>
+      <c r="B18" s="39"/>
+      <c r="C18" s="39"/>
+      <c r="D18" s="39"/>
+      <c r="E18" s="39"/>
+      <c r="F18" s="40"/>
+      <c r="G18" s="39"/>
+      <c r="H18" s="39"/>
+      <c r="I18" s="42">
+        <f>1-SUM(H15:H17)/SUM($D15:$D17)</f>
+        <v>0</v>
+      </c>
+      <c r="J18" s="39"/>
+      <c r="K18" s="39"/>
+      <c r="L18" s="42">
+        <f>1-SUM(K15:K17)/SUM($D15:$D17)</f>
+        <v>0.1428571428571429</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>101</v>
+      </c>
+      <c r="B19" t="s">
+        <v>107</v>
+      </c>
+      <c r="C19" t="s">
+        <v>111</v>
+      </c>
+      <c r="D19" t="s">
+        <v>112</v>
+      </c>
+      <c r="E19" t="s">
+        <v>113</v>
+      </c>
+      <c r="F19" s="40"/>
+      <c r="G19" t="s">
+        <v>114</v>
+      </c>
+      <c r="H19" t="s">
+        <v>113</v>
+      </c>
+      <c r="I19" s="40"/>
+      <c r="J19" t="s">
+        <v>114</v>
+      </c>
+      <c r="K19" t="s">
+        <v>113</v>
+      </c>
+      <c r="L19" s="40"/>
+    </row>
+    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A20" s="36" t="s">
+        <v>106</v>
+      </c>
+      <c r="B20" s="36" t="s">
+        <v>108</v>
+      </c>
+      <c r="C20" s="36">
+        <v>1</v>
+      </c>
+      <c r="D20" s="36">
+        <v>3</v>
+      </c>
+      <c r="E20" s="36">
+        <f>$D20-C20</f>
+        <v>2</v>
+      </c>
+      <c r="F20" s="40"/>
+      <c r="G20" s="36">
+        <v>0.3</v>
+      </c>
+      <c r="H20" s="36">
+        <f>$D20-G20</f>
+        <v>2.7</v>
+      </c>
+      <c r="I20" s="41">
+        <f>1-H20/$D20</f>
+        <v>9.9999999999999978E-2</v>
+      </c>
+      <c r="J20" s="36">
+        <f>G20</f>
+        <v>0.3</v>
+      </c>
+      <c r="K20" s="36">
+        <f>$D20-J20</f>
+        <v>2.7</v>
+      </c>
+      <c r="L20" s="41">
+        <f>1-K20/$D20</f>
+        <v>9.9999999999999978E-2</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A21" s="37" t="s">
+        <v>106</v>
+      </c>
+      <c r="B21" s="37" t="s">
+        <v>109</v>
+      </c>
+      <c r="C21" s="37">
+        <v>1</v>
+      </c>
+      <c r="D21" s="37">
+        <v>3</v>
+      </c>
+      <c r="E21" s="37">
+        <f t="shared" ref="E21:E22" si="9">$D21-C21</f>
+        <v>2</v>
+      </c>
+      <c r="F21" s="40"/>
+      <c r="G21" s="37">
+        <v>0.1</v>
+      </c>
+      <c r="H21" s="37">
+        <f>$D21-G21</f>
+        <v>2.9</v>
+      </c>
+      <c r="I21" s="41">
+        <f t="shared" ref="I21:I22" si="10">1-H21/$D21</f>
+        <v>3.3333333333333326E-2</v>
+      </c>
+      <c r="J21" s="37">
+        <f>G21</f>
+        <v>0.1</v>
+      </c>
+      <c r="K21" s="37">
+        <f>$D21-J21</f>
+        <v>2.9</v>
+      </c>
+      <c r="L21" s="41">
+        <f t="shared" ref="L21:L22" si="11">1-K21/$D21</f>
+        <v>3.3333333333333326E-2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A22" s="35" t="s">
+        <v>106</v>
+      </c>
+      <c r="B22" s="35" t="s">
+        <v>110</v>
+      </c>
+      <c r="C22" s="35">
+        <v>1</v>
+      </c>
+      <c r="D22" s="35">
+        <v>2</v>
+      </c>
+      <c r="E22" s="35">
+        <f t="shared" si="9"/>
+        <v>1</v>
+      </c>
+      <c r="F22" s="40"/>
+      <c r="G22" s="35">
+        <v>0.3</v>
+      </c>
+      <c r="H22" s="35">
+        <f>$D22-G22</f>
+        <v>1.7</v>
+      </c>
+      <c r="I22" s="41">
+        <f t="shared" si="10"/>
+        <v>0.15000000000000002</v>
+      </c>
+      <c r="J22" s="35">
+        <f>G22+1</f>
+        <v>1.3</v>
+      </c>
+      <c r="K22" s="35">
+        <f>$D22-J22</f>
+        <v>0.7</v>
+      </c>
+      <c r="L22" s="41">
+        <f t="shared" si="11"/>
+        <v>0.65</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A23" s="38"/>
+      <c r="B23" s="38"/>
+      <c r="C23" s="38"/>
+      <c r="D23" s="38"/>
+      <c r="E23" s="38"/>
+      <c r="F23" s="40"/>
+      <c r="G23" s="38"/>
+      <c r="H23" s="38"/>
+      <c r="I23" s="42">
+        <f>1-SUM(H20:H22)/SUM($D20:$D22)</f>
+        <v>8.7500000000000022E-2</v>
+      </c>
+      <c r="J23" s="38"/>
+      <c r="K23" s="38"/>
+      <c r="L23" s="42">
+        <f>1-SUM(K20:K22)/SUM($D20:$D22)</f>
+        <v>0.21250000000000002</v>
+      </c>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="E1:E1048576 H1:H1048576">
+    <cfRule type="dataBar" priority="3">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF638EC6"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{EFFE0158-A5C0-4387-BE4F-77857BCF59A7}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K1:K1048576">
+    <cfRule type="dataBar" priority="1">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF638EC6"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{192BB334-06C5-4EA6-B6BA-F8298D9BE3CC}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
+      <x14:conditionalFormattings>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{EFFE0158-A5C0-4387-BE4F-77857BCF59A7}">
+            <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:borderColor rgb="FF638EC6"/>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:negativeBorderColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>E1:E1048576 H1:H1048576</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{192BB334-06C5-4EA6-B6BA-F8298D9BE3CC}">
+            <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:borderColor rgb="FF638EC6"/>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:negativeBorderColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>K1:K1048576</xm:sqref>
+        </x14:conditionalFormatting>
+      </x14:conditionalFormattings>
+    </ext>
+  </extLst>
+</worksheet>
 </file>